--- a/BWI/bestwine_output/bestwine_Croatia.xlsx
+++ b/BWI/bestwine_output/bestwine_Croatia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA190"/>
+  <dimension ref="A1:AA191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -21336,6 +21336,95 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteka Greenside</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Vinoteka Greenside</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>91163</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Zadar</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Zadarska županija, Općina Zadar</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>1 Akcije Maslenice</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://greenside.hr</t>
+        </is>
+      </c>
+      <c r="J191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="inlineStr"/>
+      <c r="L191" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="inlineStr"/>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>greenside.zd@gmail.com</t>
+        </is>
+      </c>
+      <c r="O191" s="2" t="inlineStr"/>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>09712250861</t>
+        </is>
+      </c>
+      <c r="R191" s="2" t="inlineStr"/>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/greensidezd</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/green_side_zadar</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="2" t="inlineStr"/>
+      <c r="W191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr"/>
+      <c r="Y191" s="2" t="inlineStr"/>
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
